--- a/artfynd/A 37237-2023 artfynd.xlsx
+++ b/artfynd/A 37237-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37237-2023 artfynd.xlsx
+++ b/artfynd/A 37237-2023 artfynd.xlsx
@@ -675,50 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91131933</v>
+        <v>101511371</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillkullberget-Kilhöjden, Jmt</t>
+          <t>Lillkullberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518921.9759745444</v>
+        <v>518872</v>
       </c>
       <c r="R2" t="n">
-        <v>7011223.778886082</v>
+        <v>7011271</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-18</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-18</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,75 +767,61 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalktallskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91131935</v>
+        <v>104846956</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillkullberget-Kilhöjden, Jmt</t>
+          <t>Lillkullberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518921.9759745444</v>
+        <v>518481</v>
       </c>
       <c r="R3" t="n">
-        <v>7011223.778886082</v>
+        <v>7011427</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,40 +864,30 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalktallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91131967</v>
+        <v>101511427</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,34 +895,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219795</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillkullberget-Kilhöjden, Jmt</t>
+          <t>Lillkullberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518506.077005495</v>
+        <v>518918</v>
       </c>
       <c r="R4" t="n">
-        <v>7011321.900259332</v>
+        <v>7011247</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,22 +951,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-18</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-06-18</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,78 +977,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalktallskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91131964</v>
+        <v>96227449</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillkullberget-Kilhöjden, Jmt</t>
+          <t>Lillkullberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518506.077005495</v>
+        <v>518674</v>
       </c>
       <c r="R5" t="n">
-        <v>7011321.900259332</v>
+        <v>7011313</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,40 +1074,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalktallskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96227464</v>
+        <v>96227450</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518876.346542856</v>
+        <v>518659</v>
       </c>
       <c r="R6" t="n">
-        <v>7011229.372347832</v>
+        <v>7011326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,19 +1158,9 @@
           <t>2021-07-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,15 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96227465</v>
+        <v>96227452</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518863.0038607254</v>
+        <v>518550</v>
       </c>
       <c r="R7" t="n">
-        <v>7011195.030625641</v>
+        <v>7011479</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,19 +1255,9 @@
           <t>2021-07-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,15 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96227466</v>
+        <v>96227453</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518868.0857636906</v>
+        <v>518594</v>
       </c>
       <c r="R8" t="n">
-        <v>7011175.223336134</v>
+        <v>7011482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,19 +1352,9 @@
           <t>2021-07-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,12 +1384,7 @@
         <v>96227454</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518726.9743529924</v>
+        <v>518727</v>
       </c>
       <c r="R9" t="n">
-        <v>7011452.558736281</v>
+        <v>7011452</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,19 +1449,9 @@
           <t>2021-07-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,37 +1478,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96227451</v>
+        <v>96227464</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1647,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518560.2010704276</v>
+        <v>518877</v>
       </c>
       <c r="R10" t="n">
-        <v>7011330.326089073</v>
+        <v>7011230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,19 +1546,9 @@
           <t>2021-07-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,15 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96227453</v>
+        <v>96227465</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,10 +1610,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518594.5411648069</v>
+        <v>518863</v>
       </c>
       <c r="R11" t="n">
-        <v>7011481.545267469</v>
+        <v>7011195</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,19 +1643,9 @@
           <t>2021-07-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,15 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96227452</v>
+        <v>96227466</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518549.4140542566</v>
+        <v>518868</v>
       </c>
       <c r="R12" t="n">
-        <v>7011479.031364816</v>
+        <v>7011175</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,19 +1740,9 @@
           <t>2021-07-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,53 +1769,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96227450</v>
+        <v>91131935</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillkullberget, Jmt</t>
+          <t>Lillkullberget-Kilhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518659.5451849514</v>
+        <v>518922</v>
       </c>
       <c r="R13" t="n">
-        <v>7011325.489532665</v>
+        <v>7011224</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,22 +1834,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,69 +1850,73 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalktallskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96227449</v>
+        <v>91131964</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillkullberget, Jmt</t>
+          <t>Lillkullberget-Kilhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518673.6123771456</v>
+        <v>518506</v>
       </c>
       <c r="R14" t="n">
-        <v>7011312.947935745</v>
+        <v>7011322</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2125,22 +1940,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,31 +1956,35 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalktallskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101511371</v>
+        <v>96227451</v>
       </c>
       <c r="B15" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2183,38 +1992,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillkullberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518872.0382690931</v>
+        <v>518560</v>
       </c>
       <c r="R15" t="n">
-        <v>7011271.274530851</v>
+        <v>7011330</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2238,22 +2046,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,49 +2066,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101511567</v>
+        <v>101511656</v>
       </c>
       <c r="B16" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,14 +2111,14 @@
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillkullberget, Jmt</t>
+          <t>Lillkullberget , Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518936.2445975727</v>
+        <v>518936</v>
       </c>
       <c r="R16" t="n">
-        <v>7011254.068509799</v>
+        <v>7011269</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2357,7 +2150,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2160,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,52 +2187,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101511427</v>
+        <v>104846948</v>
       </c>
       <c r="B17" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219795</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillkullberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518917.3267371139</v>
+        <v>518868</v>
       </c>
       <c r="R17" t="n">
-        <v>7011246.744165834</v>
+        <v>7011298</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2466,22 +2252,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,31 +2272,30 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101511656</v>
+        <v>104846958</v>
       </c>
       <c r="B18" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2542,18 +2317,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillkullberget , Jmt</t>
+          <t>Lillkullberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518936.1572428162</v>
+        <v>518497</v>
       </c>
       <c r="R18" t="n">
-        <v>7011268.945412845</v>
+        <v>7011309</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2580,22 +2353,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,27 +2373,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104846957</v>
+        <v>91131967</v>
       </c>
       <c r="B19" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,14 +2420,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillkullberget, Jmt</t>
+          <t>Lillkullberget-Kilhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518485.8224025256</v>
+        <v>518506</v>
       </c>
       <c r="R19" t="n">
-        <v>7011311.415177377</v>
+        <v>7011322</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2692,22 +2454,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,35 +2470,35 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalktallskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104846958</v>
+        <v>104846957</v>
       </c>
       <c r="B20" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,21 +2506,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2778,10 +2530,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518496.6721054806</v>
+        <v>518486</v>
       </c>
       <c r="R20" t="n">
-        <v>7011308.772450075</v>
+        <v>7011311</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2811,19 +2563,9 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,15 +2596,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104846948</v>
+        <v>91131933</v>
       </c>
       <c r="B21" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,34 +2607,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillkullberget, Jmt</t>
+          <t>Lillkullberget-Kilhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518867.817142717</v>
+        <v>518922</v>
       </c>
       <c r="R21" t="n">
-        <v>7011298.299476781</v>
+        <v>7011224</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2924,22 +2661,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2950,70 +2677,72 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalktallskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104846956</v>
+        <v>101511567</v>
       </c>
       <c r="B22" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lillkullberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518481.0956060688</v>
+        <v>518936</v>
       </c>
       <c r="R22" t="n">
-        <v>7011427.247521646</v>
+        <v>7011254</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3040,22 +2769,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,19 +2799,15 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37237-2023 artfynd.xlsx
+++ b/artfynd/A 37237-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101511371</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104846956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101511427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96227449</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96227450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96227452</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96227453</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96227454</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96227464</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96227465</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96227466</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131935</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1978,6 +2043,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131964</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96227451</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101511656</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2285,6 +2365,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104846948</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2386,6 +2471,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104846958</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131967</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2593,6 +2688,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104846957</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2699,6 +2799,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131933</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2808,8 +2913,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101511567</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>